--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -59067,27 +59067,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -59097,26 +59097,26 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L215" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -59134,22 +59134,22 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>8.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q215" t="n">
-        <v>41.2</v>
+        <v>33.7</v>
       </c>
       <c r="R215" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S215" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T215" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U215" t="n">
-        <v>24.9</v>
+        <v>50</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -59188,7 +59188,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr"/>
@@ -59200,17 +59200,17 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
@@ -59220,12 +59220,12 @@
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -59235,80 +59235,104 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>96.2648</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>0.3798</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA215" t="inlineStr"/>
-      <c r="BB215" t="inlineStr"/>
-      <c r="BC215" t="inlineStr"/>
-      <c r="BD215" t="inlineStr"/>
-      <c r="BE215" t="inlineStr"/>
-      <c r="BF215" t="inlineStr"/>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ215" t="inlineStr"/>
@@ -59319,27 +59343,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -59349,22 +59373,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -59382,26 +59406,26 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>31.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q216" t="n">
-        <v>33.7</v>
+        <v>41.2</v>
       </c>
       <c r="R216" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S216" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T216" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U216" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -59415,7 +59439,7 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -59440,7 +59464,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr"/>
@@ -59457,12 +59481,12 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -59472,12 +59496,12 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -59487,104 +59511,80 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>28.83</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>99.7927</t>
+          <t>96.2648</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.3798</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>0.0927</t>
-        </is>
-      </c>
-      <c r="BA216" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB216" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC216" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD216" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE216" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF216" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr"/>
+      <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr"/>
@@ -59595,27 +59595,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59625,26 +59625,26 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -59658,26 +59658,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>17.5</v>
+        <v>31.4</v>
       </c>
       <c r="Q217" t="n">
-        <v>40.2</v>
+        <v>33.7</v>
       </c>
       <c r="R217" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S217" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T217" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U217" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59716,7 +59716,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr"/>
@@ -59733,12 +59733,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -59748,12 +59748,12 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -59763,80 +59763,104 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>99.2705</t>
+          <t>99.7927</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="BA217" t="inlineStr"/>
-      <c r="BB217" t="inlineStr"/>
-      <c r="BC217" t="inlineStr"/>
-      <c r="BD217" t="inlineStr"/>
-      <c r="BE217" t="inlineStr"/>
-      <c r="BF217" t="inlineStr"/>
+          <t>0.0927</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -59847,27 +59871,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -59877,22 +59901,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -59914,22 +59938,22 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>31.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q218" t="n">
-        <v>14</v>
+        <v>40.2</v>
       </c>
       <c r="R218" t="n">
-        <v>38.7</v>
+        <v>25.4</v>
       </c>
       <c r="S218" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T218" t="n">
         <v>75</v>
       </c>
       <c r="U218" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
@@ -59943,7 +59967,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -59968,7 +59992,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -59985,27 +60009,27 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -60015,104 +60039,80 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>99.2705</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.1149</t>
-        </is>
-      </c>
-      <c r="BA218" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="BB218" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BC218" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="BD218" t="inlineStr">
-        <is>
-          <t>0.338</t>
-        </is>
-      </c>
-      <c r="BE218" t="inlineStr">
-        <is>
-          <t>0.106</t>
-        </is>
-      </c>
-      <c r="BF218" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr"/>
+      <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -60123,12 +60123,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -60172,7 +60172,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -60190,22 +60190,22 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>21</v>
+        <v>31.3</v>
       </c>
       <c r="Q219" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="R219" t="n">
         <v>38.7</v>
       </c>
       <c r="S219" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T219" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U219" t="n">
-        <v>22.4</v>
+        <v>36</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -60244,7 +60244,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr"/>
@@ -60261,27 +60261,27 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -60291,67 +60291,67 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>98.4504</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
@@ -60399,27 +60399,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -60429,26 +60429,26 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L220" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -60466,22 +60466,22 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Q220" t="n">
-        <v>38</v>
+        <v>14.3</v>
       </c>
       <c r="R220" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S220" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T220" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U220" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -60520,7 +60520,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -60542,22 +60542,22 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
@@ -60567,104 +60567,104 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>99.0171</t>
+          <t>98.4504</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE220" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ220" t="inlineStr"/>
@@ -60675,27 +60675,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -60705,17 +60705,17 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -60724,7 +60724,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -60738,26 +60738,26 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q221" t="n">
-        <v>45.5</v>
+        <v>38</v>
       </c>
       <c r="R221" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S221" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T221" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U221" t="n">
-        <v>18</v>
+        <v>60.7</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -60813,7 +60813,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI221" t="inlineStr">
@@ -60823,17 +60823,17 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -60843,104 +60843,104 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>99.0171</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.0946</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE221" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ221" t="inlineStr"/>
@@ -60951,27 +60951,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60981,17 +60981,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -61000,7 +61000,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -61018,22 +61018,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>10.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q222" t="n">
-        <v>60.9</v>
+        <v>45.5</v>
       </c>
       <c r="R222" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S222" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T222" t="n">
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -61072,7 +61072,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -61089,12 +61089,12 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -61104,119 +61104,119 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>96.5058</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE222" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -61227,27 +61227,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -61257,26 +61257,26 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L223" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -61294,22 +61294,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q223" t="n">
-        <v>22.7</v>
+        <v>60.9</v>
       </c>
       <c r="R223" t="n">
         <v>27.6</v>
       </c>
       <c r="S223" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T223" t="n">
         <v>50</v>
       </c>
       <c r="U223" t="n">
-        <v>57.8</v>
+        <v>7</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -61348,7 +61348,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -61365,134 +61365,134 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>96.5058</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61503,12 +61503,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -61566,11 +61566,11 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q224" t="n">
         <v>22.7</v>
@@ -61579,13 +61579,13 @@
         <v>27.6</v>
       </c>
       <c r="S224" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T224" t="n">
         <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61624,7 +61624,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61641,22 +61641,22 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -61671,67 +61671,67 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
@@ -61779,27 +61779,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -61809,17 +61809,17 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -61842,26 +61842,26 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q225" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R225" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T225" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
@@ -61927,17 +61927,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -61947,104 +61947,104 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE225" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ225" t="inlineStr"/>
@@ -62055,24 +62055,24 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62085,17 +62085,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62104,7 +62104,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -62122,22 +62122,22 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q226" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R226" t="n">
         <v>23.2</v>
       </c>
       <c r="S226" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T226" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U226" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62176,7 +62176,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -62193,12 +62193,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -62208,12 +62208,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62223,97 +62223,97 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -62331,27 +62331,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -62366,12 +62366,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62398,13 +62398,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q227" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R227" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S227" t="n">
         <v>47.9</v>
@@ -62413,7 +62413,7 @@
         <v>75</v>
       </c>
       <c r="U227" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62469,134 +62469,134 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62607,12 +62607,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -62656,7 +62656,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -62670,26 +62670,26 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q228" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R228" t="n">
         <v>22.6</v>
       </c>
       <c r="S228" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T228" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -62728,7 +62728,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62745,7 +62745,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
@@ -62755,17 +62755,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -62775,67 +62775,67 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
@@ -62883,27 +62883,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -62913,26 +62913,26 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -62946,26 +62946,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="Q229" t="n">
-        <v>45.5</v>
+        <v>39</v>
       </c>
       <c r="R229" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T229" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U229" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63004,7 +63004,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63021,134 +63021,134 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/12, 0 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>86.08</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>95.6415</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.2894</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -63159,27 +63159,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -63189,22 +63189,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -63226,22 +63226,22 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>8.4</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="R230" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S230" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -63297,134 +63297,134 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 0/12, 0 HR</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>86.08</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>95.6415</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.2894</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ230" t="inlineStr"/>
@@ -63435,27 +63435,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63465,17 +63465,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63484,7 +63484,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63502,22 +63502,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63556,7 +63556,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63573,134 +63573,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -59067,27 +59067,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -59097,26 +59097,26 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L215" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -59134,22 +59134,22 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="Q215" t="n">
-        <v>33.7</v>
+        <v>41.2</v>
       </c>
       <c r="R215" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S215" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T215" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U215" t="n">
-        <v>50</v>
+        <v>24.9</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -59188,7 +59188,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr"/>
@@ -59200,32 +59200,32 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -59235,104 +59235,80 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.83</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>96.2648</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3798</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>0.029</t>
-        </is>
-      </c>
-      <c r="BA215" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB215" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC215" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD215" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE215" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF215" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ215" t="inlineStr"/>
@@ -59343,27 +59319,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -59373,22 +59349,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -59406,26 +59382,26 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>8.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q216" t="n">
-        <v>41.2</v>
+        <v>33.7</v>
       </c>
       <c r="R216" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S216" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T216" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U216" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -59439,7 +59415,7 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -59464,7 +59440,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr"/>
@@ -59481,12 +59457,12 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -59496,12 +59472,12 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -59511,80 +59487,104 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>96.2648</t>
+          <t>99.7927</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>0.3798</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA216" t="inlineStr"/>
-      <c r="BB216" t="inlineStr"/>
-      <c r="BC216" t="inlineStr"/>
-      <c r="BD216" t="inlineStr"/>
-      <c r="BE216" t="inlineStr"/>
-      <c r="BF216" t="inlineStr"/>
+          <t>0.0927</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr"/>
@@ -59595,27 +59595,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59625,26 +59625,26 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -59658,26 +59658,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>31.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q217" t="n">
-        <v>33.7</v>
+        <v>40.2</v>
       </c>
       <c r="R217" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S217" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T217" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U217" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59716,7 +59716,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr"/>
@@ -59733,12 +59733,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -59748,12 +59748,12 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -59763,104 +59763,80 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>99.7927</t>
+          <t>99.2705</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.0927</t>
-        </is>
-      </c>
-      <c r="BA217" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB217" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC217" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD217" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE217" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF217" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr"/>
+      <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -59871,27 +59847,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -59901,22 +59877,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -59938,22 +59914,22 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>17.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q218" t="n">
-        <v>40.2</v>
+        <v>14</v>
       </c>
       <c r="R218" t="n">
-        <v>25.4</v>
+        <v>38.7</v>
       </c>
       <c r="S218" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T218" t="n">
         <v>75</v>
       </c>
       <c r="U218" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
@@ -59967,7 +59943,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -59992,7 +59968,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -60009,27 +59985,27 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -60039,80 +60015,104 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>99.2705</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="BA218" t="inlineStr"/>
-      <c r="BB218" t="inlineStr"/>
-      <c r="BC218" t="inlineStr"/>
-      <c r="BD218" t="inlineStr"/>
-      <c r="BE218" t="inlineStr"/>
-      <c r="BF218" t="inlineStr"/>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>0.338</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>0.106</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -60123,12 +60123,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -60172,7 +60172,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -60190,22 +60190,22 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>31.3</v>
+        <v>21</v>
       </c>
       <c r="Q219" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="R219" t="n">
         <v>38.7</v>
       </c>
       <c r="S219" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T219" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U219" t="n">
-        <v>36</v>
+        <v>22.4</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -60244,7 +60244,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr"/>
@@ -60261,27 +60261,27 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -60291,67 +60291,67 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>98.4504</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
@@ -60399,27 +60399,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -60429,26 +60429,26 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L220" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -60466,22 +60466,22 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Q220" t="n">
-        <v>14.3</v>
+        <v>38</v>
       </c>
       <c r="R220" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S220" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T220" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U220" t="n">
-        <v>22.4</v>
+        <v>60.7</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -60520,7 +60520,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -60542,22 +60542,22 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
@@ -60567,104 +60567,104 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>98.4504</t>
+          <t>99.0171</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.0946</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE220" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ220" t="inlineStr"/>
@@ -60675,27 +60675,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -60705,17 +60705,17 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -60724,7 +60724,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -60738,26 +60738,26 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q221" t="n">
-        <v>38</v>
+        <v>45.5</v>
       </c>
       <c r="R221" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S221" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T221" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U221" t="n">
-        <v>60.7</v>
+        <v>18</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -60813,7 +60813,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI221" t="inlineStr">
@@ -60823,17 +60823,17 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -60843,104 +60843,104 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>99.0171</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE221" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ221" t="inlineStr"/>
@@ -60951,27 +60951,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60981,17 +60981,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -61000,7 +61000,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -61018,22 +61018,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>6.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q222" t="n">
-        <v>45.5</v>
+        <v>60.9</v>
       </c>
       <c r="R222" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S222" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T222" t="n">
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -61072,7 +61072,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -61089,12 +61089,12 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -61104,119 +61104,119 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>96.5058</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="BE222" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -61227,27 +61227,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -61257,26 +61257,26 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L223" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -61294,22 +61294,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>10.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q223" t="n">
-        <v>60.9</v>
+        <v>22.7</v>
       </c>
       <c r="R223" t="n">
         <v>27.6</v>
       </c>
       <c r="S223" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T223" t="n">
         <v>50</v>
       </c>
       <c r="U223" t="n">
-        <v>7</v>
+        <v>57.8</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -61348,7 +61348,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -61365,134 +61365,134 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>96.5058</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61503,12 +61503,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -61566,11 +61566,11 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>36.8</v>
       </c>
       <c r="Q224" t="n">
         <v>22.7</v>
@@ -61579,13 +61579,13 @@
         <v>27.6</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
         <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>31.9</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61624,7 +61624,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61641,22 +61641,22 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -61671,67 +61671,67 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
@@ -61779,27 +61779,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -61809,17 +61809,17 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -61842,26 +61842,26 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q225" t="n">
-        <v>22.7</v>
+        <v>39.3</v>
       </c>
       <c r="R225" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T225" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>21.5</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
@@ -61927,17 +61927,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -61947,104 +61947,104 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE225" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ225" t="inlineStr"/>
@@ -62055,24 +62055,24 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62085,17 +62085,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62104,7 +62104,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -62122,22 +62122,22 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>23.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>35.6</v>
       </c>
       <c r="R226" t="n">
         <v>23.2</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62176,7 +62176,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -62193,12 +62193,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -62208,12 +62208,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62223,97 +62223,97 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -62331,27 +62331,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -62366,12 +62366,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62398,13 +62398,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>37.8</v>
       </c>
       <c r="R227" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="S227" t="n">
         <v>47.9</v>
@@ -62413,7 +62413,7 @@
         <v>75</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62469,134 +62469,134 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62607,12 +62607,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -62656,7 +62656,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -62670,26 +62670,26 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>26</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>39</v>
       </c>
       <c r="R228" t="n">
         <v>22.6</v>
       </c>
       <c r="S228" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T228" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>36</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -62728,7 +62728,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62745,7 +62745,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
@@ -62755,17 +62755,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -62775,67 +62775,67 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
@@ -62883,27 +62883,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -62913,26 +62913,26 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -62946,26 +62946,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>45.5</v>
       </c>
       <c r="R229" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63004,7 +63004,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63021,12 +63021,12 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -63036,119 +63036,119 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 0/12, 0 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>86.08</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>95.6415</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2894</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -63159,27 +63159,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -63189,22 +63189,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -63226,22 +63226,22 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>8.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q230" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="R230" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S230" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U230" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -63297,134 +63297,134 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/12, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>86.08</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>95.6415</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.2894</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ230" t="inlineStr"/>
@@ -63435,27 +63435,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63465,17 +63465,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63484,7 +63484,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63502,22 +63502,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="Q231" t="n">
-        <v>40</v>
+        <v>33.7</v>
       </c>
       <c r="R231" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S231" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U231" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63556,7 +63556,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63573,134 +63573,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22_full.xlsx
@@ -61607,27 +61607,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -61637,17 +61637,17 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -61656,7 +61656,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -61670,26 +61670,26 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q224" t="n">
-        <v>22.7</v>
+        <v>25.9</v>
       </c>
       <c r="R224" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>67</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61728,7 +61728,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61745,27 +61745,27 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -61775,42 +61775,42 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>98.2082</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -61820,59 +61820,59 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -61883,12 +61883,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -61913,7 +61913,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -61946,11 +61946,11 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q225" t="n">
         <v>22.7</v>
@@ -61959,13 +61959,13 @@
         <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T225" t="n">
         <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -62004,7 +62004,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr"/>
@@ -62021,22 +62021,22 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -62051,67 +62051,67 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
@@ -62159,27 +62159,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -62189,17 +62189,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62222,26 +62222,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R226" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62297,7 +62297,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
@@ -62307,17 +62307,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62327,104 +62327,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -62435,24 +62435,24 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62465,17 +62465,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62484,7 +62484,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -62502,22 +62502,22 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R227" t="n">
         <v>23.2</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T227" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62573,12 +62573,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -62588,12 +62588,12 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -62603,97 +62603,97 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -62711,27 +62711,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -62746,12 +62746,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -62778,13 +62778,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R228" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S228" t="n">
         <v>47.9</v>
@@ -62793,7 +62793,7 @@
         <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62849,134 +62849,134 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -62987,12 +62987,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -63017,7 +63017,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -63036,7 +63036,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -63050,26 +63050,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R229" t="n">
         <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63108,7 +63108,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63125,7 +63125,7 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
@@ -63135,17 +63135,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -63155,67 +63155,67 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
@@ -63263,24 +63263,24 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>2026-08-23T00:40:00Z</t>
@@ -63298,12 +63298,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -63312,7 +63312,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -63326,14 +63326,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>26</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R230" t="n">
         <v>22.6</v>
@@ -63342,10 +63342,10 @@
         <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63384,7 +63384,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr"/>
@@ -63401,27 +63401,27 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -63431,97 +63431,97 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -63539,27 +63539,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63569,17 +63569,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63588,7 +63588,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63606,22 +63606,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63660,7 +63660,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63677,134 +63677,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>
@@ -63815,27 +63815,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63850,12 +63850,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -63878,26 +63878,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q232" t="n">
-        <v>39</v>
+        <v>33.7</v>
       </c>
       <c r="R232" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S232" t="n">
         <v>59.8</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U232" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr"/>
@@ -63953,134 +63953,134 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>96.7655</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -64091,27 +64091,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -64126,12 +64126,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -64154,26 +64154,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="Q233" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="R233" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S233" t="n">
         <v>59.8</v>
       </c>
       <c r="T233" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -64229,134 +64229,134 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.8947</t>
+          <t>96.7655</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3684</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
       <c r="BH233" t="inlineStr"/>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -64367,27 +64367,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -64397,17 +64397,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -64416,7 +64416,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -64434,22 +64434,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Q234" t="n">
-        <v>39.3</v>
+        <v>21.5</v>
       </c>
       <c r="R234" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S234" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T234" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U234" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -64488,7 +64488,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -64505,12 +64505,12 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -64520,12 +64520,12 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -64535,104 +64535,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>97.4351</t>
+          <t>97.8947</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3684</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -64643,27 +64643,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -64673,17 +64673,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -64706,26 +64706,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q235" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S235" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U235" t="n">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -64781,12 +64781,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -64796,12 +64796,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -64811,104 +64811,104 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>96.3935</t>
+          <t>97.4351</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.1036</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.1217</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64919,27 +64919,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64949,22 +64949,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64982,26 +64982,26 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>27.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q236" t="n">
-        <v>21.9</v>
+        <v>35</v>
       </c>
       <c r="R236" t="n">
         <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U236" t="n">
-        <v>17.3</v>
+        <v>27.7</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65057,12 +65057,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -65072,119 +65072,119 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>99.4468</t>
+          <t>96.3935</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.4195</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1036</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.1217</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65195,27 +65195,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65225,26 +65225,26 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65258,26 +65258,26 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>18.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>42.6</v>
+        <v>21.9</v>
       </c>
       <c r="R237" t="n">
         <v>27.6</v>
       </c>
       <c r="S237" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>5.1</v>
+        <v>17.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65316,7 +65316,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr"/>
@@ -65333,12 +65333,12 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65348,119 +65348,119 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>98.1355</t>
+          <t>99.4468</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3881</t>
+          <t>0.4195</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1118</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -65471,22 +65471,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -65501,17 +65501,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -65520,7 +65520,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -65534,26 +65534,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>36.8</v>
+        <v>42.6</v>
       </c>
       <c r="R238" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S238" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>43.2</v>
+        <v>5.1</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -65609,27 +65609,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -65639,104 +65639,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>99.1019</t>
+          <t>98.1355</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3881</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>0.1118</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2629</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -65747,22 +65747,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -65782,12 +65782,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -65814,22 +65814,22 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>20.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q239" t="n">
-        <v>25.9</v>
+        <v>36.8</v>
       </c>
       <c r="R239" t="n">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="S239" t="n">
         <v>40.2</v>
       </c>
       <c r="T239" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>40.3</v>
+        <v>43.2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr"/>
@@ -65885,27 +65885,27 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -65915,104 +65915,104 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.1019</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.2629</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>
